--- a/ksoft_old/docs/records/Expense_Types_Imports_Records.xlsx
+++ b/ksoft_old/docs/records/Expense_Types_Imports_Records.xlsx
@@ -1927,13 +1927,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0581CBB2-B15D-4FF4-9BFE-1C41AFD86561}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04214952-D03C-4BCE-AD5F-FF3DC2703855}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F250FD1A-9140-4C32-8419-6BD99C674E8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDA8B5F-6E8C-42D8-A71C-3C3776DBC979}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF857687-DC1F-4348-8684-0C16B0CB7056}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5352AE4-5D7B-451B-A839-D31CBD3A00D6}"/>
 </file>
--- a/ksoft_old/docs/records/Expense_Types_Imports_Records.xlsx
+++ b/ksoft_old/docs/records/Expense_Types_Imports_Records.xlsx
@@ -1927,13 +1927,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04214952-D03C-4BCE-AD5F-FF3DC2703855}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB74767-8346-4361-B636-24C80AD43F77}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDA8B5F-6E8C-42D8-A71C-3C3776DBC979}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F99C24EF-4F4A-47E6-AF58-80BC04AEB40E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5352AE4-5D7B-451B-A839-D31CBD3A00D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9437011B-8EDA-4B89-9877-89420D94D160}"/>
 </file>
--- a/ksoft_old/docs/records/Expense_Types_Imports_Records.xlsx
+++ b/ksoft_old/docs/records/Expense_Types_Imports_Records.xlsx
@@ -1927,13 +1927,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB74767-8346-4361-B636-24C80AD43F77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0581CBB2-B15D-4FF4-9BFE-1C41AFD86561}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F99C24EF-4F4A-47E6-AF58-80BC04AEB40E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F250FD1A-9140-4C32-8419-6BD99C674E8F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9437011B-8EDA-4B89-9877-89420D94D160}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF857687-DC1F-4348-8684-0C16B0CB7056}"/>
 </file>